--- a/data_processed/results_XGB_kWh_electricity_per_capitatenure.xlsx
+++ b/data_processed/results_XGB_kWh_electricity_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9017" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9108" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.23471069335938</v>
+        <v>71.88661193847656</v>
       </c>
       <c r="D2" t="n">
-        <v>7.863722324371338</v>
+        <v>8.420249938964844</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>134.4866638183594</v>
+        <v>146.7052764892578</v>
       </c>
       <c r="D3" t="n">
-        <v>16.21170234680176</v>
+        <v>17.18393707275391</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.55285453796387</v>
+        <v>30.25588607788086</v>
       </c>
       <c r="D4" t="n">
-        <v>3.803540706634521</v>
+        <v>3.543943881988525</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.99371719360352</v>
+        <v>30.18257522583008</v>
       </c>
       <c r="D5" t="n">
-        <v>3.615594625473022</v>
+        <v>3.535356760025024</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.01534175872803</v>
+        <v>20.18578338623047</v>
       </c>
       <c r="D6" t="n">
-        <v>1.810025334358215</v>
+        <v>2.364408731460571</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.69800758361816</v>
+        <v>18.06721687316895</v>
       </c>
       <c r="D7" t="n">
-        <v>2.495042562484741</v>
+        <v>2.11625599861145</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.24291515350342</v>
+        <v>263.3853149414062</v>
       </c>
       <c r="D8" t="n">
-        <v>1.83745813369751</v>
+        <v>30.85094833374023</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>291.2862854003906</v>
+        <v>80.97303009033203</v>
       </c>
       <c r="D9" t="n">
-        <v>35.11312484741211</v>
+        <v>9.484563827514648</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>cars_per_adult</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.11116027832031</v>
+        <v>109.1654205322266</v>
       </c>
       <c r="D10" t="n">
-        <v>9.295370101928711</v>
+        <v>12.78680515289307</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +595,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>heatpump_pc</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>141.4721984863281</v>
+        <v>11.10202980041504</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05377388000488</v>
+        <v>1.30040717124939</v>
       </c>
     </row>
     <row r="12">
@@ -611,14 +611,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>heatpump_pc</t>
+          <t>solarcapacity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.47141170501709</v>
+        <v>71.82579803466797</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9006417989730835</v>
+        <v>8.413125991821289</v>
       </c>
     </row>
   </sheetData>

--- a/data_processed/results_XGB_kWh_electricity_per_capitatenure.xlsx
+++ b/data_processed/results_XGB_kWh_electricity_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9108" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9032" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71.88661193847656</v>
+        <v>72.45114135742188</v>
       </c>
       <c r="D2" t="n">
-        <v>8.420249938964844</v>
+        <v>8.59119701385498</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>146.7052764892578</v>
+        <v>243.6275787353516</v>
       </c>
       <c r="D3" t="n">
-        <v>17.18393707275391</v>
+        <v>28.88915824890137</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.25588607788086</v>
+        <v>91.77292633056641</v>
       </c>
       <c r="D4" t="n">
-        <v>3.543943881988525</v>
+        <v>10.88235855102539</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.18257522583008</v>
+        <v>182.8445129394531</v>
       </c>
       <c r="D5" t="n">
-        <v>3.535356760025024</v>
+        <v>21.68155288696289</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.18578338623047</v>
+        <v>36.70813751220703</v>
       </c>
       <c r="D6" t="n">
-        <v>2.364408731460571</v>
+        <v>4.352820873260498</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.06721687316895</v>
+        <v>25.17313766479492</v>
       </c>
       <c r="D7" t="n">
-        <v>2.11625599861145</v>
+        <v>2.985009908676147</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>263.3853149414062</v>
+        <v>16.34331321716309</v>
       </c>
       <c r="D8" t="n">
-        <v>30.85094833374023</v>
+        <v>1.937976717948914</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.97303009033203</v>
+        <v>19.25658416748047</v>
       </c>
       <c r="D9" t="n">
-        <v>9.484563827514648</v>
+        <v>2.283430099487305</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>heatpump_pc</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>109.1654205322266</v>
+        <v>14.59282493591309</v>
       </c>
       <c r="D10" t="n">
-        <v>12.78680515289307</v>
+        <v>1.730405211448669</v>
       </c>
     </row>
     <row r="11">
@@ -595,30 +595,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>heatpump_pc</t>
+          <t>solarcapacity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.10202980041504</v>
+        <v>140.5481872558594</v>
       </c>
       <c r="D11" t="n">
-        <v>1.30040717124939</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>solarcapacity</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>71.82579803466797</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8.413125991821289</v>
+        <v>16.66608810424805</v>
       </c>
     </row>
   </sheetData>
